--- a/example_data/metadata.xlsx
+++ b/example_data/metadata.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.leeuwerik\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{431875C0-A5D5-4C09-B47A-89AE82DC4457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26ACC3F0-16A2-4CF0-8953-F6CFA7DA9C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rhodes_metadata" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2267" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2268" uniqueCount="274">
   <si>
     <t>ARAF001</t>
   </si>
@@ -844,6 +845,9 @@
   </si>
   <si>
     <t>Clade</t>
+  </si>
+  <si>
+    <t>`Empty` sheet 2</t>
   </si>
 </sst>
 </file>
@@ -11332,4 +11336,22 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3953F869-36B8-4C2E-B964-F9A75DCFFBB7}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/example_data/metadata.xlsx
+++ b/example_data/metadata.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.leeuwerik\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26ACC3F0-16A2-4CF0-8953-F6CFA7DA9C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{735EBC5E-C2B9-4CA9-B5FE-D1F4A3999252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Rhodes_metadata" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2268" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2049" uniqueCount="271">
   <si>
     <t>ARAF001</t>
   </si>
@@ -754,18 +754,12 @@
     <t>0.5</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>0.25</t>
   </si>
   <si>
     <t>0.06</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>0.125</t>
   </si>
   <si>
@@ -842,9 +836,6 @@
   </si>
   <si>
     <t>Sample id</t>
-  </si>
-  <si>
-    <t>Clade</t>
   </si>
   <si>
     <t>`Empty` sheet 2</t>
@@ -1392,9 +1383,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B784A48F-1F8E-4306-A5AC-E98E6E4E60C2}" name="Table3" displayName="Table3" ref="A1:N219" totalsRowShown="0">
-  <autoFilter ref="A1:N219" xr:uid="{B784A48F-1F8E-4306-A5AC-E98E6E4E60C2}"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B784A48F-1F8E-4306-A5AC-E98E6E4E60C2}" name="Table3" displayName="Table3" ref="A1:M219" totalsRowShown="0">
+  <autoFilter ref="A1:M219" xr:uid="{B784A48F-1F8E-4306-A5AC-E98E6E4E60C2}"/>
+  <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{CF124BC1-B399-4314-B1A0-9DD59500E680}" name="Sample id"/>
     <tableColumn id="2" xr3:uid="{A6B6B1C3-717F-43E6-ADFE-E8C9D0B98BF2}" name="Latitude"/>
     <tableColumn id="3" xr3:uid="{FD921ACB-F5B2-4F57-98F5-CE35C1DDC797}" name="Longitude"/>
@@ -1407,7 +1398,6 @@
     <tableColumn id="11" xr3:uid="{15192BC2-D331-4477-AEA3-34C9E7F5E6BA}" name="Itraconazole MIC"/>
     <tableColumn id="12" xr3:uid="{A5A258C9-9A34-48D8-89C8-292ABD606AEF}" name="Voriconazole MIC"/>
     <tableColumn id="13" xr3:uid="{4CDCD4B7-0F9E-4FD2-A19D-9D9CD7A8B9A9}" name="Posaconazole MIC"/>
-    <tableColumn id="14" xr3:uid="{1EDCAC2B-0FBF-4F74-B546-52B7FAA3F3FC}" name="Clade"/>
     <tableColumn id="9" xr3:uid="{A1C7384F-512E-4CB3-9508-023A27AE2C8F}" name="DAPCcluster"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1711,7 +1701,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N219"/>
+  <dimension ref="A1:M219"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -1732,51 +1722,48 @@
     <col min="19" max="19" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G1" t="s">
+        <v>258</v>
+      </c>
+      <c r="H1" t="s">
         <v>259</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
+        <v>262</v>
+      </c>
+      <c r="J1" t="s">
         <v>263</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
+        <v>264</v>
+      </c>
+      <c r="L1" t="s">
+        <v>265</v>
+      </c>
+      <c r="M1" t="s">
         <v>260</v>
       </c>
-      <c r="H1" t="s">
-        <v>261</v>
-      </c>
-      <c r="I1" t="s">
-        <v>264</v>
-      </c>
-      <c r="J1" t="s">
-        <v>265</v>
-      </c>
-      <c r="K1" t="s">
-        <v>266</v>
-      </c>
-      <c r="L1" t="s">
-        <v>267</v>
-      </c>
-      <c r="M1" t="s">
-        <v>272</v>
-      </c>
-      <c r="N1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1814,13 +1801,10 @@
         <v>241</v>
       </c>
       <c r="M2" t="s">
-        <v>242</v>
-      </c>
-      <c r="N2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1858,13 +1842,10 @@
         <v>241</v>
       </c>
       <c r="M3" t="s">
-        <v>242</v>
-      </c>
-      <c r="N3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1896,19 +1877,16 @@
         <v>1</v>
       </c>
       <c r="K4" t="s">
+        <v>242</v>
+      </c>
+      <c r="L4" t="s">
         <v>243</v>
       </c>
-      <c r="L4" t="s">
-        <v>244</v>
-      </c>
       <c r="M4" t="s">
-        <v>245</v>
-      </c>
-      <c r="N4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1943,16 +1921,13 @@
         <v>241</v>
       </c>
       <c r="L5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M5" t="s">
-        <v>242</v>
-      </c>
-      <c r="N5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1984,19 +1959,16 @@
         <v>241</v>
       </c>
       <c r="K6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M6" t="s">
-        <v>245</v>
-      </c>
-      <c r="N6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -2031,16 +2003,13 @@
         <v>241</v>
       </c>
       <c r="L7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M7" t="s">
-        <v>242</v>
-      </c>
-      <c r="N7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -2075,16 +2044,13 @@
         <v>2</v>
       </c>
       <c r="L8" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="M8" t="s">
-        <v>242</v>
-      </c>
-      <c r="N8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -2122,13 +2088,10 @@
         <v>241</v>
       </c>
       <c r="M9" t="s">
-        <v>242</v>
-      </c>
-      <c r="N9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -2163,16 +2126,13 @@
         <v>4</v>
       </c>
       <c r="L10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M10" t="s">
-        <v>242</v>
-      </c>
-      <c r="N10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -2207,16 +2167,13 @@
         <v>2</v>
       </c>
       <c r="L11" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M11" t="s">
-        <v>242</v>
-      </c>
-      <c r="N11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -2254,13 +2211,10 @@
         <v>1</v>
       </c>
       <c r="M12" t="s">
-        <v>242</v>
-      </c>
-      <c r="N12" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -2295,16 +2249,13 @@
         <v>4</v>
       </c>
       <c r="L13" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M13" t="s">
-        <v>242</v>
-      </c>
-      <c r="N13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -2339,16 +2290,13 @@
         <v>4</v>
       </c>
       <c r="L14" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M14" t="s">
-        <v>242</v>
-      </c>
-      <c r="N14" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -2383,16 +2331,13 @@
         <v>4</v>
       </c>
       <c r="L15" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M15" t="s">
-        <v>242</v>
-      </c>
-      <c r="N15" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -2427,16 +2372,13 @@
         <v>1</v>
       </c>
       <c r="L16" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M16" t="s">
-        <v>242</v>
-      </c>
-      <c r="N16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -2471,16 +2413,13 @@
         <v>1</v>
       </c>
       <c r="L17" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M17" t="s">
-        <v>245</v>
-      </c>
-      <c r="N17" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -2515,16 +2454,13 @@
         <v>2</v>
       </c>
       <c r="L18" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M18" t="s">
-        <v>242</v>
-      </c>
-      <c r="N18" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -2559,16 +2495,13 @@
         <v>1</v>
       </c>
       <c r="L19" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M19" t="s">
-        <v>242</v>
-      </c>
-      <c r="N19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -2603,16 +2536,13 @@
         <v>2</v>
       </c>
       <c r="L20" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M20" t="s">
-        <v>242</v>
-      </c>
-      <c r="N20" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>31</v>
       </c>
@@ -2647,16 +2577,13 @@
         <v>2</v>
       </c>
       <c r="L21" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M21" t="s">
-        <v>242</v>
-      </c>
-      <c r="N21" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>32</v>
       </c>
@@ -2685,22 +2612,19 @@
         <v>12</v>
       </c>
       <c r="J22" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K22" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L22" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M22" t="s">
-        <v>245</v>
-      </c>
-      <c r="N22" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>33</v>
       </c>
@@ -2735,16 +2659,13 @@
         <v>2</v>
       </c>
       <c r="L23" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M23" t="s">
-        <v>242</v>
-      </c>
-      <c r="N23" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -2779,16 +2700,13 @@
         <v>1</v>
       </c>
       <c r="L24" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M24" t="s">
-        <v>242</v>
-      </c>
-      <c r="N24" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>35</v>
       </c>
@@ -2823,16 +2741,13 @@
         <v>2</v>
       </c>
       <c r="L25" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M25" t="s">
-        <v>245</v>
-      </c>
-      <c r="N25" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>36</v>
       </c>
@@ -2867,16 +2782,13 @@
         <v>1</v>
       </c>
       <c r="L26" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M26" t="s">
-        <v>245</v>
-      </c>
-      <c r="N26" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>37</v>
       </c>
@@ -2911,16 +2823,13 @@
         <v>1</v>
       </c>
       <c r="L27" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M27" t="s">
-        <v>242</v>
-      </c>
-      <c r="N27" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>38</v>
       </c>
@@ -2955,16 +2864,13 @@
         <v>4</v>
       </c>
       <c r="L28" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M28" t="s">
-        <v>242</v>
-      </c>
-      <c r="N28" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>39</v>
       </c>
@@ -2996,19 +2902,16 @@
         <v>240</v>
       </c>
       <c r="K29" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L29" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M29" t="s">
-        <v>245</v>
-      </c>
-      <c r="N29" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>41</v>
       </c>
@@ -3040,19 +2943,16 @@
         <v>240</v>
       </c>
       <c r="K30" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L30" t="s">
         <v>241</v>
       </c>
       <c r="M30" t="s">
-        <v>242</v>
-      </c>
-      <c r="N30" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>43</v>
       </c>
@@ -3087,16 +2987,13 @@
         <v>2</v>
       </c>
       <c r="L31" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M31" t="s">
-        <v>242</v>
-      </c>
-      <c r="N31" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>44</v>
       </c>
@@ -3131,16 +3028,13 @@
         <v>2</v>
       </c>
       <c r="L32" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M32" t="s">
-        <v>242</v>
-      </c>
-      <c r="N32" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>45</v>
       </c>
@@ -3172,19 +3066,16 @@
         <v>240</v>
       </c>
       <c r="K33" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L33">
         <v>4</v>
       </c>
       <c r="M33" t="s">
-        <v>245</v>
-      </c>
-      <c r="N33" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -3222,13 +3113,10 @@
         <v>2</v>
       </c>
       <c r="M34" t="s">
-        <v>242</v>
-      </c>
-      <c r="N34" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>48</v>
       </c>
@@ -3260,19 +3148,16 @@
         <v>240</v>
       </c>
       <c r="K35" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L35">
         <v>2</v>
       </c>
       <c r="M35" t="s">
-        <v>245</v>
-      </c>
-      <c r="N35" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>49</v>
       </c>
@@ -3304,19 +3189,16 @@
         <v>240</v>
       </c>
       <c r="K36" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L36" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="M36" t="s">
-        <v>245</v>
-      </c>
-      <c r="N36" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>50</v>
       </c>
@@ -3354,13 +3236,10 @@
         <v>1</v>
       </c>
       <c r="M37" t="s">
-        <v>245</v>
-      </c>
-      <c r="N37" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>51</v>
       </c>
@@ -3398,13 +3277,10 @@
         <v>241</v>
       </c>
       <c r="M38" t="s">
-        <v>245</v>
-      </c>
-      <c r="N38" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>52</v>
       </c>
@@ -3439,16 +3315,13 @@
         <v>2</v>
       </c>
       <c r="L39" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="M39" t="s">
-        <v>242</v>
-      </c>
-      <c r="N39" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>53</v>
       </c>
@@ -3480,19 +3353,16 @@
         <v>240</v>
       </c>
       <c r="K40" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L40">
         <v>8</v>
       </c>
       <c r="M40" t="s">
-        <v>245</v>
-      </c>
-      <c r="N40" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>54</v>
       </c>
@@ -3524,19 +3394,16 @@
         <v>240</v>
       </c>
       <c r="K41" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L41">
         <v>16</v>
       </c>
       <c r="M41" t="s">
-        <v>245</v>
-      </c>
-      <c r="N41" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>55</v>
       </c>
@@ -3568,19 +3435,16 @@
         <v>240</v>
       </c>
       <c r="K42" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L42">
         <v>8</v>
       </c>
       <c r="M42" t="s">
-        <v>245</v>
-      </c>
-      <c r="N42" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>56</v>
       </c>
@@ -3618,13 +3482,10 @@
         <v>2</v>
       </c>
       <c r="M43" t="s">
-        <v>242</v>
-      </c>
-      <c r="N43" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>57</v>
       </c>
@@ -3662,13 +3523,10 @@
         <v>1</v>
       </c>
       <c r="M44" t="s">
-        <v>245</v>
-      </c>
-      <c r="N44" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>58</v>
       </c>
@@ -3700,19 +3558,16 @@
         <v>240</v>
       </c>
       <c r="K45" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L45">
         <v>16</v>
       </c>
       <c r="M45" t="s">
-        <v>245</v>
-      </c>
-      <c r="N45" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>59</v>
       </c>
@@ -3750,13 +3605,10 @@
         <v>2</v>
       </c>
       <c r="M46" t="s">
-        <v>245</v>
-      </c>
-      <c r="N46" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>60</v>
       </c>
@@ -3794,13 +3646,10 @@
         <v>2</v>
       </c>
       <c r="M47" t="s">
-        <v>245</v>
-      </c>
-      <c r="N47" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>61</v>
       </c>
@@ -3832,19 +3681,16 @@
         <v>240</v>
       </c>
       <c r="K48" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L48">
         <v>2</v>
       </c>
       <c r="M48" t="s">
-        <v>245</v>
-      </c>
-      <c r="N48" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>63</v>
       </c>
@@ -3882,13 +3728,10 @@
         <v>1</v>
       </c>
       <c r="M49" t="s">
-        <v>245</v>
-      </c>
-      <c r="N49" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>64</v>
       </c>
@@ -3920,19 +3763,16 @@
         <v>240</v>
       </c>
       <c r="K50" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L50" t="s">
         <v>241</v>
       </c>
       <c r="M50" t="s">
-        <v>242</v>
-      </c>
-      <c r="N50" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>65</v>
       </c>
@@ -3964,19 +3804,16 @@
         <v>240</v>
       </c>
       <c r="K51" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L51">
         <v>16</v>
       </c>
       <c r="M51" t="s">
-        <v>245</v>
-      </c>
-      <c r="N51" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>66</v>
       </c>
@@ -4011,16 +3848,13 @@
         <v>1</v>
       </c>
       <c r="L52" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M52" t="s">
-        <v>245</v>
-      </c>
-      <c r="N52" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>67</v>
       </c>
@@ -4052,19 +3886,16 @@
         <v>240</v>
       </c>
       <c r="K53" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L53" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M53" t="s">
-        <v>242</v>
-      </c>
-      <c r="N53" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>68</v>
       </c>
@@ -4102,13 +3933,10 @@
         <v>241</v>
       </c>
       <c r="M54" t="s">
-        <v>242</v>
-      </c>
-      <c r="N54" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>69</v>
       </c>
@@ -4143,16 +3971,13 @@
         <v>2</v>
       </c>
       <c r="L55" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M55" t="s">
-        <v>242</v>
-      </c>
-      <c r="N55" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>70</v>
       </c>
@@ -4184,19 +4009,16 @@
         <v>240</v>
       </c>
       <c r="K56" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L56" t="s">
         <v>241</v>
       </c>
       <c r="M56" t="s">
-        <v>245</v>
-      </c>
-      <c r="N56" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>71</v>
       </c>
@@ -4228,19 +4050,16 @@
         <v>241</v>
       </c>
       <c r="K57" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L57" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M57" t="s">
-        <v>245</v>
-      </c>
-      <c r="N57" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>72</v>
       </c>
@@ -4272,19 +4091,16 @@
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L58" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M58" t="s">
-        <v>245</v>
-      </c>
-      <c r="N58" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>73</v>
       </c>
@@ -4316,19 +4132,16 @@
         <v>2</v>
       </c>
       <c r="K59" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L59" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M59" t="s">
-        <v>245</v>
-      </c>
-      <c r="N59" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>74</v>
       </c>
@@ -4360,19 +4173,16 @@
         <v>240</v>
       </c>
       <c r="K60" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L60" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="M60" t="s">
-        <v>242</v>
-      </c>
-      <c r="N60" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>75</v>
       </c>
@@ -4407,16 +4217,13 @@
         <v>8</v>
       </c>
       <c r="L61" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="M61" t="s">
-        <v>242</v>
-      </c>
-      <c r="N61" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>76</v>
       </c>
@@ -4448,19 +4255,16 @@
         <v>16</v>
       </c>
       <c r="K62" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L62" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="M62" t="s">
-        <v>242</v>
-      </c>
-      <c r="N62" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>77</v>
       </c>
@@ -4492,19 +4296,16 @@
         <v>240</v>
       </c>
       <c r="K63" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L63" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="M63" t="s">
-        <v>242</v>
-      </c>
-      <c r="N63" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>78</v>
       </c>
@@ -4536,19 +4337,16 @@
         <v>241</v>
       </c>
       <c r="K64" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L64" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M64" t="s">
-        <v>245</v>
-      </c>
-      <c r="N64" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>79</v>
       </c>
@@ -4580,19 +4378,16 @@
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L65" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M65" t="s">
-        <v>245</v>
-      </c>
-      <c r="N65" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>80</v>
       </c>
@@ -4624,19 +4419,16 @@
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L66" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M66" t="s">
-        <v>245</v>
-      </c>
-      <c r="N66" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>81</v>
       </c>
@@ -4674,13 +4466,10 @@
         <v>4</v>
       </c>
       <c r="M67" t="s">
-        <v>242</v>
-      </c>
-      <c r="N67" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>83</v>
       </c>
@@ -4718,13 +4507,10 @@
         <v>4</v>
       </c>
       <c r="M68" t="s">
-        <v>242</v>
-      </c>
-      <c r="N68" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>84</v>
       </c>
@@ -4762,13 +4548,10 @@
         <v>4</v>
       </c>
       <c r="M69" t="s">
-        <v>242</v>
-      </c>
-      <c r="N69" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>85</v>
       </c>
@@ -4806,13 +4589,10 @@
         <v>4</v>
       </c>
       <c r="M70" t="s">
-        <v>242</v>
-      </c>
-      <c r="N70" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>86</v>
       </c>
@@ -4850,13 +4630,10 @@
         <v>241</v>
       </c>
       <c r="M71" t="s">
-        <v>242</v>
-      </c>
-      <c r="N71" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>87</v>
       </c>
@@ -4891,16 +4668,13 @@
         <v>2</v>
       </c>
       <c r="L72" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="M72" t="s">
-        <v>242</v>
-      </c>
-      <c r="N72" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>88</v>
       </c>
@@ -4938,13 +4712,10 @@
         <v>241</v>
       </c>
       <c r="M73" t="s">
-        <v>242</v>
-      </c>
-      <c r="N73" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>89</v>
       </c>
@@ -4979,16 +4750,13 @@
         <v>241</v>
       </c>
       <c r="L74" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="M74" t="s">
-        <v>242</v>
-      </c>
-      <c r="N74" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>90</v>
       </c>
@@ -5026,13 +4794,10 @@
         <v>1</v>
       </c>
       <c r="M75" t="s">
-        <v>242</v>
-      </c>
-      <c r="N75" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>91</v>
       </c>
@@ -5070,13 +4835,10 @@
         <v>240</v>
       </c>
       <c r="M76" t="s">
-        <v>242</v>
-      </c>
-      <c r="N76" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>92</v>
       </c>
@@ -5111,16 +4873,13 @@
         <v>1</v>
       </c>
       <c r="L77" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="M77" t="s">
-        <v>245</v>
-      </c>
-      <c r="N77" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>93</v>
       </c>
@@ -5155,16 +4914,13 @@
         <v>241</v>
       </c>
       <c r="L78" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="M78" t="s">
-        <v>245</v>
-      </c>
-      <c r="N78" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>94</v>
       </c>
@@ -5196,19 +4952,16 @@
         <v>1</v>
       </c>
       <c r="K79" t="s">
+        <v>242</v>
+      </c>
+      <c r="L79" t="s">
         <v>243</v>
       </c>
-      <c r="L79" t="s">
-        <v>244</v>
-      </c>
       <c r="M79" t="s">
-        <v>245</v>
-      </c>
-      <c r="N79" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>95</v>
       </c>
@@ -5237,22 +4990,19 @@
         <v>12</v>
       </c>
       <c r="J80" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K80" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L80" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M80" t="s">
-        <v>245</v>
-      </c>
-      <c r="N80" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>96</v>
       </c>
@@ -5284,19 +5034,16 @@
         <v>2</v>
       </c>
       <c r="K81" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L81" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M81" t="s">
-        <v>245</v>
-      </c>
-      <c r="N81" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>97</v>
       </c>
@@ -5325,22 +5072,19 @@
         <v>12</v>
       </c>
       <c r="J82" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K82" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L82" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M82" t="s">
-        <v>245</v>
-      </c>
-      <c r="N82" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>98</v>
       </c>
@@ -5375,16 +5119,13 @@
         <v>2</v>
       </c>
       <c r="L83" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="M83" t="s">
-        <v>242</v>
-      </c>
-      <c r="N83" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>99</v>
       </c>
@@ -5413,22 +5154,19 @@
         <v>12</v>
       </c>
       <c r="J84" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K84" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L84" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M84" t="s">
-        <v>245</v>
-      </c>
-      <c r="N84" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>100</v>
       </c>
@@ -5463,16 +5201,13 @@
         <v>241</v>
       </c>
       <c r="L85" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M85" t="s">
-        <v>242</v>
-      </c>
-      <c r="N85" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>101</v>
       </c>
@@ -5501,22 +5236,19 @@
         <v>12</v>
       </c>
       <c r="J86" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K86" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L86" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M86" t="s">
-        <v>245</v>
-      </c>
-      <c r="N86" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>102</v>
       </c>
@@ -5545,22 +5277,19 @@
         <v>12</v>
       </c>
       <c r="J87" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K87" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L87" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M87" t="s">
-        <v>245</v>
-      </c>
-      <c r="N87" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>103</v>
       </c>
@@ -5589,22 +5318,19 @@
         <v>12</v>
       </c>
       <c r="J88" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K88" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L88" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M88" t="s">
-        <v>245</v>
-      </c>
-      <c r="N88" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>104</v>
       </c>
@@ -5633,22 +5359,19 @@
         <v>12</v>
       </c>
       <c r="J89" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K89" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L89" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M89" t="s">
-        <v>245</v>
-      </c>
-      <c r="N89" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>105</v>
       </c>
@@ -5677,22 +5400,19 @@
         <v>12</v>
       </c>
       <c r="J90" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K90" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L90" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M90" t="s">
-        <v>245</v>
-      </c>
-      <c r="N90" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>106</v>
       </c>
@@ -5721,22 +5441,19 @@
         <v>12</v>
       </c>
       <c r="J91" t="s">
+        <v>243</v>
+      </c>
+      <c r="K91" t="s">
         <v>244</v>
       </c>
-      <c r="K91" t="s">
-        <v>246</v>
-      </c>
       <c r="L91" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M91" t="s">
-        <v>242</v>
-      </c>
-      <c r="N91" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>107</v>
       </c>
@@ -5765,22 +5482,19 @@
         <v>12</v>
       </c>
       <c r="J92" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K92" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L92" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M92" t="s">
-        <v>245</v>
-      </c>
-      <c r="N92" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>108</v>
       </c>
@@ -5809,22 +5523,19 @@
         <v>12</v>
       </c>
       <c r="J93" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K93" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L93" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M93" t="s">
-        <v>245</v>
-      </c>
-      <c r="N93" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>109</v>
       </c>
@@ -5859,16 +5570,13 @@
         <v>2</v>
       </c>
       <c r="L94" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="M94" t="s">
-        <v>242</v>
-      </c>
-      <c r="N94" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>110</v>
       </c>
@@ -5897,22 +5605,19 @@
         <v>12</v>
       </c>
       <c r="J95" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K95" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L95" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M95" t="s">
-        <v>245</v>
-      </c>
-      <c r="N95" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>111</v>
       </c>
@@ -5941,22 +5646,19 @@
         <v>12</v>
       </c>
       <c r="J96" t="s">
+        <v>243</v>
+      </c>
+      <c r="K96" t="s">
         <v>244</v>
       </c>
-      <c r="K96" t="s">
-        <v>246</v>
-      </c>
       <c r="L96" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M96" t="s">
-        <v>245</v>
-      </c>
-      <c r="N96" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>112</v>
       </c>
@@ -5985,22 +5687,19 @@
         <v>12</v>
       </c>
       <c r="J97" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K97" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L97" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M97" t="s">
-        <v>245</v>
-      </c>
-      <c r="N97" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>113</v>
       </c>
@@ -6029,22 +5728,19 @@
         <v>12</v>
       </c>
       <c r="J98" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K98" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L98" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M98" t="s">
-        <v>245</v>
-      </c>
-      <c r="N98" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>114</v>
       </c>
@@ -6073,22 +5769,19 @@
         <v>12</v>
       </c>
       <c r="J99" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K99" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L99" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M99" t="s">
-        <v>245</v>
-      </c>
-      <c r="N99" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>115</v>
       </c>
@@ -6117,22 +5810,19 @@
         <v>12</v>
       </c>
       <c r="J100" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K100" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L100" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M100" t="s">
-        <v>245</v>
-      </c>
-      <c r="N100" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>116</v>
       </c>
@@ -6161,22 +5851,19 @@
         <v>12</v>
       </c>
       <c r="J101" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K101" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L101" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M101" t="s">
-        <v>242</v>
-      </c>
-      <c r="N101" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>117</v>
       </c>
@@ -6205,22 +5892,19 @@
         <v>12</v>
       </c>
       <c r="J102" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K102" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L102" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M102" t="s">
-        <v>245</v>
-      </c>
-      <c r="N102" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>118</v>
       </c>
@@ -6249,22 +5933,19 @@
         <v>12</v>
       </c>
       <c r="J103" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K103" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L103" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M103" t="s">
-        <v>242</v>
-      </c>
-      <c r="N103" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>119</v>
       </c>
@@ -6296,19 +5977,16 @@
         <v>240</v>
       </c>
       <c r="K104" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L104" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M104" t="s">
-        <v>245</v>
-      </c>
-      <c r="N104" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>120</v>
       </c>
@@ -6343,16 +6021,13 @@
         <v>1</v>
       </c>
       <c r="L105" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M105" t="s">
-        <v>242</v>
-      </c>
-      <c r="N105" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>121</v>
       </c>
@@ -6381,22 +6056,19 @@
         <v>12</v>
       </c>
       <c r="J106" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K106" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L106" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M106" t="s">
-        <v>245</v>
-      </c>
-      <c r="N106" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>122</v>
       </c>
@@ -6425,22 +6097,19 @@
         <v>12</v>
       </c>
       <c r="J107" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K107" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L107" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M107" t="s">
-        <v>245</v>
-      </c>
-      <c r="N107" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>123</v>
       </c>
@@ -6475,16 +6144,13 @@
         <v>2</v>
       </c>
       <c r="L108" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M108" t="s">
-        <v>242</v>
-      </c>
-      <c r="N108" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>124</v>
       </c>
@@ -6519,16 +6185,13 @@
         <v>2</v>
       </c>
       <c r="L109" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M109" t="s">
-        <v>242</v>
-      </c>
-      <c r="N109" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>125</v>
       </c>
@@ -6563,16 +6226,13 @@
         <v>2</v>
       </c>
       <c r="L110" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M110" t="s">
-        <v>242</v>
-      </c>
-      <c r="N110" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>126</v>
       </c>
@@ -6607,16 +6267,13 @@
         <v>2</v>
       </c>
       <c r="L111" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="M111" t="s">
-        <v>242</v>
-      </c>
-      <c r="N111" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>127</v>
       </c>
@@ -6645,22 +6302,19 @@
         <v>12</v>
       </c>
       <c r="J112" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K112" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L112" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M112" t="s">
-        <v>242</v>
-      </c>
-      <c r="N112" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>129</v>
       </c>
@@ -6689,22 +6343,19 @@
         <v>12</v>
       </c>
       <c r="J113" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K113" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L113" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M113" t="s">
-        <v>242</v>
-      </c>
-      <c r="N113" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>130</v>
       </c>
@@ -6733,22 +6384,19 @@
         <v>12</v>
       </c>
       <c r="J114" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K114" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L114" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M114" t="s">
-        <v>245</v>
-      </c>
-      <c r="N114" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>131</v>
       </c>
@@ -6777,22 +6425,19 @@
         <v>12</v>
       </c>
       <c r="J115" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K115" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L115" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M115" t="s">
-        <v>242</v>
-      </c>
-      <c r="N115" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>132</v>
       </c>
@@ -6827,16 +6472,13 @@
         <v>2</v>
       </c>
       <c r="L116" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="M116" t="s">
-        <v>242</v>
-      </c>
-      <c r="N116" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>133</v>
       </c>
@@ -6871,16 +6513,13 @@
         <v>2</v>
       </c>
       <c r="L117" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="M117" t="s">
-        <v>242</v>
-      </c>
-      <c r="N117" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>134</v>
       </c>
@@ -6909,22 +6548,19 @@
         <v>12</v>
       </c>
       <c r="J118" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K118" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L118" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M118" t="s">
-        <v>242</v>
-      </c>
-      <c r="N118" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>135</v>
       </c>
@@ -6959,16 +6595,13 @@
         <v>4</v>
       </c>
       <c r="L119" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M119" t="s">
-        <v>242</v>
-      </c>
-      <c r="N119" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>136</v>
       </c>
@@ -7000,19 +6633,16 @@
         <v>240</v>
       </c>
       <c r="K120" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L120">
         <v>1</v>
       </c>
       <c r="M120" t="s">
-        <v>242</v>
-      </c>
-      <c r="N120" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>137</v>
       </c>
@@ -7047,16 +6677,13 @@
         <v>1</v>
       </c>
       <c r="L121" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M121" t="s">
-        <v>242</v>
-      </c>
-      <c r="N121" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>138</v>
       </c>
@@ -7085,22 +6712,19 @@
         <v>12</v>
       </c>
       <c r="J122" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K122" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L122" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M122" t="s">
-        <v>245</v>
-      </c>
-      <c r="N122" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>139</v>
       </c>
@@ -7129,22 +6753,19 @@
         <v>12</v>
       </c>
       <c r="J123" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K123" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L123" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M123" t="s">
-        <v>245</v>
-      </c>
-      <c r="N123" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>140</v>
       </c>
@@ -7179,16 +6800,13 @@
         <v>4</v>
       </c>
       <c r="L124" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M124" t="s">
-        <v>242</v>
-      </c>
-      <c r="N124" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>141</v>
       </c>
@@ -7226,13 +6844,10 @@
         <v>241</v>
       </c>
       <c r="M125" t="s">
-        <v>242</v>
-      </c>
-      <c r="N125" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>142</v>
       </c>
@@ -7267,16 +6882,13 @@
         <v>2</v>
       </c>
       <c r="L126" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="M126" t="s">
-        <v>242</v>
-      </c>
-      <c r="N126" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>143</v>
       </c>
@@ -7311,16 +6923,13 @@
         <v>2</v>
       </c>
       <c r="L127" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M127" t="s">
-        <v>242</v>
-      </c>
-      <c r="N127" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>144</v>
       </c>
@@ -7355,16 +6964,13 @@
         <v>2</v>
       </c>
       <c r="L128" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="M128" t="s">
-        <v>242</v>
-      </c>
-      <c r="N128" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>145</v>
       </c>
@@ -7402,13 +7008,10 @@
         <v>241</v>
       </c>
       <c r="M129" t="s">
-        <v>242</v>
-      </c>
-      <c r="N129" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>146</v>
       </c>
@@ -7446,13 +7049,10 @@
         <v>241</v>
       </c>
       <c r="M130" t="s">
-        <v>242</v>
-      </c>
-      <c r="N130" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>147</v>
       </c>
@@ -7481,22 +7081,19 @@
         <v>12</v>
       </c>
       <c r="J131" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="K131" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L131" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M131" t="s">
-        <v>245</v>
-      </c>
-      <c r="N131" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>148</v>
       </c>
@@ -7531,16 +7128,13 @@
         <v>241</v>
       </c>
       <c r="L132" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M132" t="s">
-        <v>242</v>
-      </c>
-      <c r="N132" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>149</v>
       </c>
@@ -7575,16 +7169,13 @@
         <v>241</v>
       </c>
       <c r="L133" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M133" t="s">
-        <v>242</v>
-      </c>
-      <c r="N133" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>150</v>
       </c>
@@ -7613,22 +7204,19 @@
         <v>12</v>
       </c>
       <c r="J134" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K134" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L134" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M134" t="s">
-        <v>245</v>
-      </c>
-      <c r="N134" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>151</v>
       </c>
@@ -7657,22 +7245,19 @@
         <v>12</v>
       </c>
       <c r="J135" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K135" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L135" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M135" t="s">
-        <v>245</v>
-      </c>
-      <c r="N135" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>152</v>
       </c>
@@ -7701,22 +7286,19 @@
         <v>12</v>
       </c>
       <c r="J136" t="s">
+        <v>242</v>
+      </c>
+      <c r="K136" t="s">
         <v>243</v>
       </c>
-      <c r="K136" t="s">
-        <v>244</v>
-      </c>
       <c r="L136" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M136" t="s">
-        <v>245</v>
-      </c>
-      <c r="N136" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>153</v>
       </c>
@@ -7745,22 +7327,19 @@
         <v>12</v>
       </c>
       <c r="J137" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K137" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L137" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M137" t="s">
-        <v>242</v>
-      </c>
-      <c r="N137" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>154</v>
       </c>
@@ -7798,13 +7377,10 @@
         <v>241</v>
       </c>
       <c r="M138" t="s">
-        <v>242</v>
-      </c>
-      <c r="N138" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>155</v>
       </c>
@@ -7839,13 +7415,10 @@
         <v>241</v>
       </c>
       <c r="M139" t="s">
-        <v>242</v>
-      </c>
-      <c r="N139" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>156</v>
       </c>
@@ -7871,22 +7444,19 @@
         <v>6</v>
       </c>
       <c r="J140" t="s">
+        <v>242</v>
+      </c>
+      <c r="K140" t="s">
         <v>243</v>
       </c>
-      <c r="K140" t="s">
-        <v>244</v>
-      </c>
       <c r="L140" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M140" t="s">
-        <v>245</v>
-      </c>
-      <c r="N140" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>157</v>
       </c>
@@ -7921,13 +7491,10 @@
         <v>241</v>
       </c>
       <c r="M141" t="s">
-        <v>242</v>
-      </c>
-      <c r="N141" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>158</v>
       </c>
@@ -7953,22 +7520,19 @@
         <v>159</v>
       </c>
       <c r="J142" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K142" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L142" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M142" t="s">
-        <v>242</v>
-      </c>
-      <c r="N142" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>160</v>
       </c>
@@ -7994,22 +7558,19 @@
         <v>159</v>
       </c>
       <c r="J143" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K143" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L143" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M143" t="s">
-        <v>242</v>
-      </c>
-      <c r="N143" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>162</v>
       </c>
@@ -8044,13 +7605,10 @@
         <v>241</v>
       </c>
       <c r="M144" t="s">
-        <v>242</v>
-      </c>
-      <c r="N144" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>163</v>
       </c>
@@ -8079,22 +7637,19 @@
         <v>12</v>
       </c>
       <c r="J145" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K145" t="s">
+        <v>242</v>
+      </c>
+      <c r="L145" t="s">
         <v>243</v>
       </c>
-      <c r="L145" t="s">
-        <v>244</v>
-      </c>
       <c r="M145" t="s">
-        <v>242</v>
-      </c>
-      <c r="N145" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>164</v>
       </c>
@@ -8120,22 +7675,19 @@
         <v>159</v>
       </c>
       <c r="J146" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K146" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L146" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M146" t="s">
-        <v>242</v>
-      </c>
-      <c r="N146" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>165</v>
       </c>
@@ -8161,22 +7713,19 @@
         <v>159</v>
       </c>
       <c r="J147" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K147" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L147" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M147" t="s">
-        <v>242</v>
-      </c>
-      <c r="N147" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>166</v>
       </c>
@@ -8202,22 +7751,19 @@
         <v>12</v>
       </c>
       <c r="J148" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="K148" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L148" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M148" t="s">
-        <v>242</v>
-      </c>
-      <c r="N148" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>167</v>
       </c>
@@ -8243,22 +7789,19 @@
         <v>12</v>
       </c>
       <c r="J149" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K149" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L149" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M149" t="s">
-        <v>242</v>
-      </c>
-      <c r="N149" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>168</v>
       </c>
@@ -8293,16 +7836,13 @@
         <v>241</v>
       </c>
       <c r="L150" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M150" t="s">
-        <v>242</v>
-      </c>
-      <c r="N150" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>170</v>
       </c>
@@ -8337,16 +7877,13 @@
         <v>2</v>
       </c>
       <c r="L151" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M151" t="s">
-        <v>242</v>
-      </c>
-      <c r="N151" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>172</v>
       </c>
@@ -8378,19 +7915,16 @@
         <v>4</v>
       </c>
       <c r="K152" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L152" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M152" t="s">
-        <v>242</v>
-      </c>
-      <c r="N152" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>173</v>
       </c>
@@ -8425,16 +7959,13 @@
         <v>241</v>
       </c>
       <c r="L153" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M153" t="s">
-        <v>242</v>
-      </c>
-      <c r="N153" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>174</v>
       </c>
@@ -8469,16 +8000,13 @@
         <v>241</v>
       </c>
       <c r="L154" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M154" t="s">
-        <v>242</v>
-      </c>
-      <c r="N154" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>175</v>
       </c>
@@ -8513,16 +8041,13 @@
         <v>241</v>
       </c>
       <c r="L155" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M155" t="s">
-        <v>242</v>
-      </c>
-      <c r="N155" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>176</v>
       </c>
@@ -8551,22 +8076,19 @@
         <v>12</v>
       </c>
       <c r="J156" t="s">
+        <v>242</v>
+      </c>
+      <c r="K156" t="s">
+        <v>244</v>
+      </c>
+      <c r="L156" t="s">
         <v>243</v>
       </c>
-      <c r="K156" t="s">
-        <v>246</v>
-      </c>
-      <c r="L156" t="s">
-        <v>244</v>
-      </c>
       <c r="M156" t="s">
-        <v>245</v>
-      </c>
-      <c r="N156" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>177</v>
       </c>
@@ -8595,22 +8117,19 @@
         <v>12</v>
       </c>
       <c r="J157" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K157" t="s">
+        <v>242</v>
+      </c>
+      <c r="L157" t="s">
         <v>243</v>
       </c>
-      <c r="L157" t="s">
-        <v>244</v>
-      </c>
       <c r="M157" t="s">
-        <v>242</v>
-      </c>
-      <c r="N157" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>178</v>
       </c>
@@ -8639,22 +8158,19 @@
         <v>12</v>
       </c>
       <c r="J158" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K158" t="s">
+        <v>242</v>
+      </c>
+      <c r="L158" t="s">
         <v>243</v>
       </c>
-      <c r="L158" t="s">
-        <v>244</v>
-      </c>
       <c r="M158" t="s">
-        <v>245</v>
-      </c>
-      <c r="N158" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>179</v>
       </c>
@@ -8689,16 +8205,13 @@
         <v>8</v>
       </c>
       <c r="L159" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="M159" t="s">
-        <v>245</v>
-      </c>
-      <c r="N159" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>180</v>
       </c>
@@ -8727,22 +8240,19 @@
         <v>12</v>
       </c>
       <c r="J160" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K160" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L160" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M160" t="s">
-        <v>245</v>
-      </c>
-      <c r="N160" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>181</v>
       </c>
@@ -8771,22 +8281,19 @@
         <v>12</v>
       </c>
       <c r="J161" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K161" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L161" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M161" t="s">
-        <v>245</v>
-      </c>
-      <c r="N161" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>182</v>
       </c>
@@ -8815,22 +8322,19 @@
         <v>12</v>
       </c>
       <c r="J162" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K162" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L162" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="M162" t="s">
-        <v>245</v>
-      </c>
-      <c r="N162" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>183</v>
       </c>
@@ -8859,22 +8363,19 @@
         <v>12</v>
       </c>
       <c r="J163" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K163" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L163" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M163" t="s">
-        <v>245</v>
-      </c>
-      <c r="N163" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>184</v>
       </c>
@@ -8903,22 +8404,19 @@
         <v>12</v>
       </c>
       <c r="J164" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K164" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L164" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M164" t="s">
-        <v>245</v>
-      </c>
-      <c r="N164" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>185</v>
       </c>
@@ -8947,22 +8445,19 @@
         <v>12</v>
       </c>
       <c r="J165" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K165" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L165" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M165" t="s">
-        <v>245</v>
-      </c>
-      <c r="N165" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>186</v>
       </c>
@@ -8991,22 +8486,19 @@
         <v>12</v>
       </c>
       <c r="J166" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K166" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L166" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M166" t="s">
-        <v>245</v>
-      </c>
-      <c r="N166" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>187</v>
       </c>
@@ -9035,22 +8527,19 @@
         <v>12</v>
       </c>
       <c r="J167" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K167" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="L167" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M167" t="s">
-        <v>245</v>
-      </c>
-      <c r="N167" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>188</v>
       </c>
@@ -9079,22 +8568,19 @@
         <v>12</v>
       </c>
       <c r="J168" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K168" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="L168" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M168" t="s">
-        <v>245</v>
-      </c>
-      <c r="N168" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>189</v>
       </c>
@@ -9123,22 +8609,19 @@
         <v>12</v>
       </c>
       <c r="J169" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="K169" t="s">
+        <v>242</v>
+      </c>
+      <c r="L169" t="s">
         <v>243</v>
       </c>
-      <c r="L169" t="s">
-        <v>244</v>
-      </c>
       <c r="M169" t="s">
-        <v>245</v>
-      </c>
-      <c r="N169" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>190</v>
       </c>
@@ -9173,16 +8656,13 @@
         <v>2</v>
       </c>
       <c r="L170" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="M170" t="s">
-        <v>242</v>
-      </c>
-      <c r="N170" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>191</v>
       </c>
@@ -9211,22 +8691,19 @@
         <v>12</v>
       </c>
       <c r="J171" t="s">
+        <v>242</v>
+      </c>
+      <c r="K171" t="s">
+        <v>245</v>
+      </c>
+      <c r="L171" t="s">
         <v>243</v>
       </c>
-      <c r="K171" t="s">
-        <v>247</v>
-      </c>
-      <c r="L171" t="s">
-        <v>244</v>
-      </c>
       <c r="M171" t="s">
-        <v>245</v>
-      </c>
-      <c r="N171" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>192</v>
       </c>
@@ -9255,22 +8732,19 @@
         <v>12</v>
       </c>
       <c r="J172" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K172" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L172" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M172" t="s">
-        <v>245</v>
-      </c>
-      <c r="N172" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>193</v>
       </c>
@@ -9299,22 +8773,19 @@
         <v>12</v>
       </c>
       <c r="J173" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="K173" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L173" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M173" t="s">
-        <v>245</v>
-      </c>
-      <c r="N173" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>194</v>
       </c>
@@ -9343,22 +8814,19 @@
         <v>12</v>
       </c>
       <c r="J174" t="s">
+        <v>242</v>
+      </c>
+      <c r="K174" t="s">
+        <v>245</v>
+      </c>
+      <c r="L174" t="s">
         <v>243</v>
       </c>
-      <c r="K174" t="s">
-        <v>247</v>
-      </c>
-      <c r="L174" t="s">
-        <v>244</v>
-      </c>
       <c r="M174" t="s">
-        <v>245</v>
-      </c>
-      <c r="N174" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>195</v>
       </c>
@@ -9387,22 +8855,19 @@
         <v>12</v>
       </c>
       <c r="J175" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K175" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L175" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M175" t="s">
-        <v>245</v>
-      </c>
-      <c r="N175" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>196</v>
       </c>
@@ -9431,22 +8896,19 @@
         <v>12</v>
       </c>
       <c r="J176" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K176" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L176" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M176" t="s">
-        <v>245</v>
-      </c>
-      <c r="N176" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>197</v>
       </c>
@@ -9475,22 +8937,19 @@
         <v>12</v>
       </c>
       <c r="J177" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="K177" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L177" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M177" t="s">
-        <v>245</v>
-      </c>
-      <c r="N177" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>198</v>
       </c>
@@ -9519,22 +8978,19 @@
         <v>12</v>
       </c>
       <c r="J178" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K178" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L178" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M178" t="s">
-        <v>245</v>
-      </c>
-      <c r="N178" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>199</v>
       </c>
@@ -9563,22 +9019,19 @@
         <v>12</v>
       </c>
       <c r="J179" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K179" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L179" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M179" t="s">
-        <v>242</v>
-      </c>
-      <c r="N179" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>200</v>
       </c>
@@ -9607,22 +9060,19 @@
         <v>12</v>
       </c>
       <c r="J180" t="s">
+        <v>242</v>
+      </c>
+      <c r="K180" t="s">
+        <v>245</v>
+      </c>
+      <c r="L180" t="s">
         <v>243</v>
       </c>
-      <c r="K180" t="s">
-        <v>247</v>
-      </c>
-      <c r="L180" t="s">
-        <v>244</v>
-      </c>
       <c r="M180" t="s">
-        <v>242</v>
-      </c>
-      <c r="N180" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>201</v>
       </c>
@@ -9657,16 +9107,13 @@
         <v>2</v>
       </c>
       <c r="L181" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M181" t="s">
-        <v>242</v>
-      </c>
-      <c r="N181" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>202</v>
       </c>
@@ -9695,22 +9142,19 @@
         <v>12</v>
       </c>
       <c r="J182" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="K182" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L182" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M182" t="s">
-        <v>242</v>
-      </c>
-      <c r="N182" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>203</v>
       </c>
@@ -9739,22 +9183,19 @@
         <v>12</v>
       </c>
       <c r="J183" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K183" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L183" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M183" t="s">
-        <v>242</v>
-      </c>
-      <c r="N183" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>204</v>
       </c>
@@ -9783,22 +9224,19 @@
         <v>12</v>
       </c>
       <c r="J184" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K184" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L184" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M184" t="s">
-        <v>242</v>
-      </c>
-      <c r="N184" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>205</v>
       </c>
@@ -9827,22 +9265,19 @@
         <v>12</v>
       </c>
       <c r="J185" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K185" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L185" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M185" t="s">
-        <v>242</v>
-      </c>
-      <c r="N185" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>206</v>
       </c>
@@ -9871,22 +9306,19 @@
         <v>12</v>
       </c>
       <c r="J186" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K186" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L186" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="M186" t="s">
-        <v>242</v>
-      </c>
-      <c r="N186" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>207</v>
       </c>
@@ -9915,22 +9347,19 @@
         <v>12</v>
       </c>
       <c r="J187" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K187" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L187" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M187" t="s">
-        <v>242</v>
-      </c>
-      <c r="N187" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>208</v>
       </c>
@@ -9959,22 +9388,19 @@
         <v>12</v>
       </c>
       <c r="J188" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K188" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L188" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M188" t="s">
-        <v>242</v>
-      </c>
-      <c r="N188" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>209</v>
       </c>
@@ -10003,22 +9429,19 @@
         <v>12</v>
       </c>
       <c r="J189" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K189" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L189" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M189" t="s">
-        <v>245</v>
-      </c>
-      <c r="N189" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>210</v>
       </c>
@@ -10047,22 +9470,19 @@
         <v>12</v>
       </c>
       <c r="J190" t="s">
+        <v>242</v>
+      </c>
+      <c r="K190" t="s">
+        <v>242</v>
+      </c>
+      <c r="L190" t="s">
         <v>243</v>
       </c>
-      <c r="K190" t="s">
-        <v>243</v>
-      </c>
-      <c r="L190" t="s">
-        <v>244</v>
-      </c>
       <c r="M190" t="s">
-        <v>242</v>
-      </c>
-      <c r="N190" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>211</v>
       </c>
@@ -10094,16 +9514,13 @@
         <v>241</v>
       </c>
       <c r="L191" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M191" t="s">
-        <v>242</v>
-      </c>
-      <c r="N191" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>212</v>
       </c>
@@ -10138,16 +9555,13 @@
         <v>4</v>
       </c>
       <c r="L192" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M192" t="s">
-        <v>242</v>
-      </c>
-      <c r="N192" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>213</v>
       </c>
@@ -10179,16 +9593,13 @@
         <v>1</v>
       </c>
       <c r="L193" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M193" t="s">
-        <v>242</v>
-      </c>
-      <c r="N193" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>214</v>
       </c>
@@ -10217,22 +9628,19 @@
         <v>12</v>
       </c>
       <c r="J194" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="K194" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L194" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="M194" t="s">
-        <v>245</v>
-      </c>
-      <c r="N194" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>215</v>
       </c>
@@ -10261,22 +9669,19 @@
         <v>12</v>
       </c>
       <c r="J195" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K195" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L195" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M195" t="s">
-        <v>245</v>
-      </c>
-      <c r="N195" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>216</v>
       </c>
@@ -10305,22 +9710,19 @@
         <v>12</v>
       </c>
       <c r="J196" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K196" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L196" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M196" t="s">
-        <v>245</v>
-      </c>
-      <c r="N196" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>217</v>
       </c>
@@ -10349,22 +9751,19 @@
         <v>12</v>
       </c>
       <c r="J197" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K197" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L197" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M197" t="s">
-        <v>245</v>
-      </c>
-      <c r="N197" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>218</v>
       </c>
@@ -10390,22 +9789,19 @@
         <v>12</v>
       </c>
       <c r="J198" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K198" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L198" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="M198" t="s">
-        <v>242</v>
-      </c>
-      <c r="N198" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>219</v>
       </c>
@@ -10434,22 +9830,19 @@
         <v>12</v>
       </c>
       <c r="J199" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K199" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L199" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M199" t="s">
-        <v>245</v>
-      </c>
-      <c r="N199" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>220</v>
       </c>
@@ -10478,22 +9871,19 @@
         <v>12</v>
       </c>
       <c r="J200" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K200" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L200" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M200" t="s">
-        <v>245</v>
-      </c>
-      <c r="N200" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>221</v>
       </c>
@@ -10522,22 +9912,19 @@
         <v>159</v>
       </c>
       <c r="J201" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K201" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L201" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M201" t="s">
-        <v>242</v>
-      </c>
-      <c r="N201" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>222</v>
       </c>
@@ -10566,22 +9953,19 @@
         <v>159</v>
       </c>
       <c r="J202" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K202" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L202" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M202" t="s">
-        <v>242</v>
-      </c>
-      <c r="N202" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>223</v>
       </c>
@@ -10616,16 +10000,13 @@
         <v>2</v>
       </c>
       <c r="L203" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="M203" t="s">
-        <v>242</v>
-      </c>
-      <c r="N203" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>224</v>
       </c>
@@ -10654,22 +10035,19 @@
         <v>159</v>
       </c>
       <c r="J204" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K204" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L204" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M204" t="s">
-        <v>242</v>
-      </c>
-      <c r="N204" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>225</v>
       </c>
@@ -10698,22 +10076,19 @@
         <v>12</v>
       </c>
       <c r="J205" t="s">
+        <v>242</v>
+      </c>
+      <c r="K205" t="s">
+        <v>242</v>
+      </c>
+      <c r="L205" t="s">
         <v>243</v>
       </c>
-      <c r="K205" t="s">
-        <v>243</v>
-      </c>
-      <c r="L205" t="s">
-        <v>244</v>
-      </c>
       <c r="M205" t="s">
-        <v>245</v>
-      </c>
-      <c r="N205" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>226</v>
       </c>
@@ -10751,13 +10126,10 @@
         <v>1</v>
       </c>
       <c r="M206" t="s">
-        <v>242</v>
-      </c>
-      <c r="N206" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>227</v>
       </c>
@@ -10795,13 +10167,10 @@
         <v>241</v>
       </c>
       <c r="M207" t="s">
-        <v>242</v>
-      </c>
-      <c r="N207" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>228</v>
       </c>
@@ -10839,13 +10208,10 @@
         <v>241</v>
       </c>
       <c r="M208" t="s">
-        <v>242</v>
-      </c>
-      <c r="N208" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>229</v>
       </c>
@@ -10874,22 +10240,19 @@
         <v>159</v>
       </c>
       <c r="J209" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K209" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L209" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M209" t="s">
-        <v>242</v>
-      </c>
-      <c r="N209" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>230</v>
       </c>
@@ -10918,22 +10281,19 @@
         <v>159</v>
       </c>
       <c r="J210" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K210" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L210" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M210" t="s">
-        <v>242</v>
-      </c>
-      <c r="N210" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>231</v>
       </c>
@@ -10962,22 +10322,19 @@
         <v>159</v>
       </c>
       <c r="J211" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K211" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L211" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M211" t="s">
-        <v>245</v>
-      </c>
-      <c r="N211" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>232</v>
       </c>
@@ -11006,22 +10363,19 @@
         <v>159</v>
       </c>
       <c r="J212" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K212" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L212" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M212" t="s">
-        <v>242</v>
-      </c>
-      <c r="N212" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>233</v>
       </c>
@@ -11050,22 +10404,19 @@
         <v>159</v>
       </c>
       <c r="J213" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K213" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L213" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M213" t="s">
-        <v>242</v>
-      </c>
-      <c r="N213" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>234</v>
       </c>
@@ -11094,22 +10445,19 @@
         <v>159</v>
       </c>
       <c r="J214" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K214" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L214" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M214" t="s">
-        <v>245</v>
-      </c>
-      <c r="N214" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>235</v>
       </c>
@@ -11138,22 +10486,19 @@
         <v>159</v>
       </c>
       <c r="J215" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K215" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L215" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M215" t="s">
-        <v>242</v>
-      </c>
-      <c r="N215" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>236</v>
       </c>
@@ -11182,22 +10527,19 @@
         <v>159</v>
       </c>
       <c r="J216" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K216" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L216" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M216" t="s">
-        <v>242</v>
-      </c>
-      <c r="N216" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>237</v>
       </c>
@@ -11226,22 +10568,19 @@
         <v>159</v>
       </c>
       <c r="J217" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K217" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L217" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M217" t="s">
-        <v>245</v>
-      </c>
-      <c r="N217" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>238</v>
       </c>
@@ -11270,22 +10609,19 @@
         <v>159</v>
       </c>
       <c r="J218" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K218" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L218" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M218" t="s">
-        <v>245</v>
-      </c>
-      <c r="N218" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>239</v>
       </c>
@@ -11323,9 +10659,6 @@
         <v>241</v>
       </c>
       <c r="M219" t="s">
-        <v>242</v>
-      </c>
-      <c r="N219" t="s">
         <v>5</v>
       </c>
     </row>
@@ -11348,7 +10681,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
